--- a/stories/arbres/ATOM-LAN.SON.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honorine est dans la cour de la ferme avec papa. Un son : ouah. Papa dit : c'est un son. Quel nom ? Honorine dit : le chien. Un son : cot cot. Honorine dit le nom : la poule. L'eau de l'auge cloche. Honorine dit : l'eau. Papa dit : on entend un son. On dit le nom.</t>
+          <t>Honorine est dans la cour de la ferme avec papa. Un son : ouah. C'est un son. Quel nom ? Le chien. Un son : cot cot. Honorine dit le nom : la poule. L'eau de l'auge cloche. L'eau. On entend un son. On dit le nom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine est dans la cour de la ferme avec papa. Un son : ouah.
+papa|C'est un son. Quel nom ?
+enfant-f|Le chien.
+narrateur|Un son : cot cot. Honorine dit le nom : la poule. L'eau de l'auge cloche.
+enfant-f|L'eau.
+papa|On entend un son. On dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine a entendu un son. Elle a dit le nom. Chien. Poule. Eau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le seau. Honorine écoute encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 papa|On entend un son. On dit le nom.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|Honorine entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,11 @@
           <t>narrateur|Honorine a entendu un son. Elle a dit le nom. Chien. Poule. Eau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1848,7 @@
           <t>narrateur|Papa range le seau. Honorine écoute encore.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Honorine nomme les sons de la cour</t>
+          <t>La cour de Victorina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La paille colle au portail. Victorina nomme le chien, la poule, l'eau. Papa range le seau.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honorine est dans la cour de la ferme avec papa. Un son : ouah. C'est un son. Quel nom ? Le chien. Un son : cot cot. Honorine dit le nom : la poule. L'eau de l'auge cloche. L'eau. On entend un son. On dit le nom.</t>
+          <t>De la paille colle au portail de bois. Les pierres de la cour sont encore fraîches. Un seau sent le lait tiède. Une hirondelle passe au-dessus du toit. Les bottes de papa font un bruit sourd. Ça sent le foin et la terre. Victorina, on écoute la cour. En ce moment, Victorina s'arrête près de l'auge. L'auge est ronde et un peu humide. Un son arrive. Ouah ouah. C'est un son. Quel nom ? Le chien. Oui. Le nom du son, c'est le chien. Le chien remue la queue près du portail. Son collier cliquette. Il est content, papa. Oui. Un autre son. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. La poule picore près de la paille. Papa pose le seau. L'eau de l'auge cloche. Glou. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Son. Nom. Victorina répète tout bas. Chien. Poule. Eau. Bravo, Victorina. Tu as dit le nom. Tu as fait du bon travail. Le chien s'assoit dans un carré de soleil. La paille craque sous les pieds. Ça craque, papa. Oui. La paille fait un son. Le son a un nom. La paille. Oui. Le seau sent encore le lait. Tu as fini d'écouter ? Encore un peu. D'accord. L'hirondelle passe une seconde fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Honorine est dans la cour de la ferme avec papa. Un son : ouah.
-papa|C'est un son. Quel nom ?
+          <t>narrateur|De la paille colle au portail de bois.
+narrateur|Les pierres de la cour sont encore fraîches.
+narrateur|Un seau sent le lait tiède.
+narrateur|Une hirondelle passe au-dessus du toit.
+narrateur|Les bottes de papa font un bruit sourd.
+narrateur|Ça sent le foin et la terre.
+papa|Victorina, on écoute la cour.
+narrateur|En ce moment, Victorina s'arrête près de l'auge.
+narrateur|L'auge est ronde et un peu humide.
+narrateur|Un son arrive.
+narrateur|Ouah ouah.
+papa|C'est un son.
+papa|Quel nom ?
 enfant-f|Le chien.
-narrateur|Un son : cot cot. Honorine dit le nom : la poule. L'eau de l'auge cloche.
+papa|Oui.
+papa|Le nom du son, c'est le chien.
+narrateur|Le chien remue la queue près du portail.
+narrateur|Son collier cliquette.
+enfant-f|Il est content, papa.
+papa|Oui.
+narrateur|Un autre son.
+narrateur|Cot cot.
+papa|Encore un son.
+papa|Quel nom ?
+enfant-f|La poule.
+papa|Oui.
+papa|Le nom du son, c'est la poule.
+narrateur|La poule picore près de la paille.
+narrateur|Papa pose le seau.
+narrateur|L'eau de l'auge cloche.
+narrateur|Glou.
+papa|Un son.
+papa|Quel nom ?
 enfant-f|L'eau.
-papa|On entend un son. On dit le nom.</t>
+papa|Oui.
+papa|On entend un son.
+papa|On dit le nom.
+enfant-f|Son.
+enfant-f|Nom.
+narrateur|Victorina répète tout bas.
+enfant-f|Chien.
+enfant-f|Poule.
+enfant-f|Eau.
+papa|Bravo, Victorina.
+papa|Tu as dit le nom.
+papa|Tu as fait du bon travail.
+narrateur|Le chien s'assoit dans un carré de soleil.
+narrateur|La paille craque sous les pieds.
+enfant-f|Ça craque, papa.
+papa|Oui.
+papa|La paille fait un son.
+papa|Le son a un nom.
+enfant-f|La paille.
+papa|Oui.
+narrateur|Le seau sent encore le lait.
+papa|Tu as fini d'écouter ?
+enfant-f|Encore un peu.
+papa|D'accord.
+narrateur|L'hirondelle passe une seconde fois.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Honorine entend un bruit. C'est quoi ?</t>
+          <t>Victorina entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,7 +1570,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Honorine entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Victorina entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1533,7 +1599,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Honorine a entendu un son. Elle a dit le nom. Chien. Poule. Eau.</t>
+          <t>Victorina a entendu un son. Elle a dit le nom. Chien. Poule. Eau. Tu as nommé le son ? Oui, papa. Bravo. Tu as fait du bon travail. Le chien respire tout près. Victorina pose la main sur le bois du portail. Il est rêche. Oui. On entend un son. On dit le nom. Le chien. Oui. L'eau tremble encore dans l'auge. Elle tremble. Oui. On a entendu des sons. On a dit les noms. Chien, poule, eau. Bravo. Le foin sent encore bon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,7 +1743,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Honorine a entendu un son. Elle a dit le nom. Chien. Poule. Eau.</t>
+          <t>narrateur|Victorina a entendu un son.
+narrateur|Elle a dit le nom.
+narrateur|Chien.
+narrateur|Poule.
+narrateur|Eau.
+papa|Tu as nommé le son ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le chien respire tout près.
+narrateur|Victorina pose la main sur le bois du portail.
+enfant-f|Il est rêche.
+papa|Oui.
+papa|On entend un son.
+papa|On dit le nom.
+enfant-f|Le chien.
+papa|Oui.
+narrateur|L'eau tremble encore dans l'auge.
+enfant-f|Elle tremble.
+papa|Oui.
+papa|On a entendu des sons.
+papa|On a dit les noms.
+enfant-f|Chien, poule, eau.
+papa|Bravo.
+narrateur|Le foin sent encore bon.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1709,7 +1799,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le seau. Honorine écoute encore.</t>
+          <t>On range le seau ? Oui. Papa range le seau contre le mur. Victorina écoute encore. Une poule rentre sous le hangar. Tu as fini d'écouter la cour ? Oui, papa. Merci. Bravo. Le collier du chien cliquette une dernière fois. La paille reste collée au portail. Tu as nommé le son, Victorina. Oui. Les pierres de la cour restent fraîches. Le chien suit jusqu'au hangar.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1845,7 +1935,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le seau. Honorine écoute encore.</t>
+          <t>papa|On range le seau ?
+enfant-f|Oui.
+narrateur|Papa range le seau contre le mur.
+narrateur|Victorina écoute encore.
+narrateur|Une poule rentre sous le hangar.
+papa|Tu as fini d'écouter la cour ?
+enfant-f|Oui, papa.
+papa|Merci.
+papa|Bravo.
+narrateur|Le collier du chien cliquette une dernière fois.
+narrateur|La paille reste collée au portail.
+papa|Tu as nommé le son, Victorina.
+enfant-f|Oui.
+narrateur|Les pierres de la cour restent fraîches.
+narrateur|Le chien suit jusqu'au hangar.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1873,7 +1977,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Chien, poule, eau. Bravo, Victorina. La cour redevient calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2013,7 +2117,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit le nom.
+papa|Oui.
+papa|Chien, poule, eau.
+papa|Bravo, Victorina.
+narrateur|La cour redevient calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2035,7 +2144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2182,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>De la paille colle au portail de bois. Les pierres de la cour sont encore fraîches. Un seau sent le lait tiède. Une hirondelle passe au-dessus du toit. Les bottes de papa font un bruit sourd. Ça sent le foin et la terre. Victorina, on écoute la cour. En ce moment, Victorina s'arrête près de l'auge. L'auge est ronde et un peu humide. Un son arrive. Ouah ouah. C'est un son. Quel nom ? Le chien. Oui. Le nom du son, c'est le chien. Le chien remue la queue près du portail. Son collier cliquette. Il est content, papa. Oui. Un autre son. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. La poule picore près de la paille. Papa pose le seau. L'eau de l'auge cloche. Glou. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Son. Nom. Victorina répète tout bas. Chien. Poule. Eau. Bravo, Victorina. Tu as dit le nom. Tu as fait du bon travail. Le chien s'assoit dans un carré de soleil. La paille craque sous les pieds. Ça craque, papa. Oui. La paille fait un son. Le son a un nom. La paille. Oui. Le seau sent encore le lait. Tu as fini d'écouter ? Encore un peu. D'accord. L'hirondelle passe une seconde fois.</t>
+          <t>De la paille colle au portail de bois. Les pierres de la cour sont encore fraîches. Un seau sent le lait tiède. Une hirondelle passe au-dessus du toit. Les bottes de papa font un bruit sourd. Ça sent le foin et la terre. Victorina, on écoute la cour. En ce moment, Victorina s'arrête près de l'auge. L'auge est ronde et un peu humide. Un son arrive. Ouah ouah. C'est un son. Quel nom ? Le chien. Oui. Le nom du son, c'est le chien. Le chien remue la queue près du portail. Son collier cliquette. Il est content, papa. Oui. Un autre son. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. La poule picore près de la paille. Papa pose le seau. L'eau de l'auge cloche. Glou. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Son. Nom. Victorina répète tout bas. Chien. Poule. Eau. Bravo, Victorina. Tu as dit le nom. Le chien s'assoit dans un carré de soleil. La paille craque sous les pieds. Ça craque, papa. Oui. La paille fait un son. Le son a un nom. La paille. Oui. Le seau sent encore le lait. Tu as fini d'écouter ? Encore un peu. D'accord. L'hirondelle passe une seconde fois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honorine est dans la cour de la ferme avec papa. Un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt; : ouah. Papa dit : c'est un son. Quel nom ? Honorine dit : le chien. Un son : cot cot. Honorine dit le nom : la poule. L'eau de l'auge cloche. Honorine dit : l'eau. Papa dit : on entend un son. On dit le nom.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>De la paille colle au portail de bois. Les pierres de la cour sont encore fraîches. Un seau sent le lait tiède. Une hirondelle passe au-dessus du toit. Les bottes de papa font un bruit sourd. Ça sent le foin et la terre. Victorina, on écoute la cour. En ce moment, Victorina s'arrête près de l'auge. L'auge est ronde et un peu humide. Un son arrive. Ouah ouah. C'est un son. Quel nom ? Le chien. Oui. Le nom du son, c'est le chien. Le chien remue la queue près du portail. Son collier cliquette. Il est content, papa. Oui. Un autre son. Cot cot. Encore un son. Quel nom ? La poule. Oui. Le nom du son, c'est la poule. La poule picore près de la paille. Papa pose le seau. L'eau de l'auge cloche. Glou. Un son. Quel nom ? L'eau. Oui. On entend un son. On dit le nom. Son. Nom. Victorina répète tout bas. Chien. Poule. Eau. Bravo, Victorina. Tu as dit le nom. Le chien s'assoit dans un carré de soleil. La paille craque sous les pieds. Ça craque, papa. Oui. La paille fait un son. Le son a un nom. La paille. Oui. Le seau sent encore le lait. Tu as fini d'écouter ? Encore un peu. D'accord. L'hirondelle passe une seconde fois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1369,7 +1369,6 @@
 enfant-f|Eau.
 papa|Bravo, Victorina.
 papa|Tu as dit le nom.
-papa|Tu as fait du bon travail.
 narrateur|Le chien s'assoit dans un carré de soleil.
 narrateur|La paille craque sous les pieds.
 enfant-f|Ça craque, papa.
@@ -1419,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honorine entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1574,7 +1573,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1599,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a entendu un son. Elle a dit le nom. Chien. Poule. Eau. Tu as nommé le son ? Oui, papa. Bravo. Tu as fait du bon travail. Le chien respire tout près. Victorina pose la main sur le bois du portail. Il est rêche. Oui. On entend un son. On dit le nom. Le chien. Oui. L'eau tremble encore dans l'auge. Elle tremble. Oui. On a entendu des sons. On a dit les noms. Chien, poule, eau. Bravo. Le foin sent encore bon.</t>
+          <t>Victorina a entendu un son. Elle a dit le nom. Chien. Poule. Eau. Tu as nommé le son ? Oui, papa. Bravo. Le chien respire tout près. Victorina pose la main sur le bois du portail. Il est rêche. Oui. On entend un son. On dit le nom. Le chien. Oui. L'eau tremble encore dans l'auge. Elle tremble. Oui. On a entendu des sons. On a dit les noms. Chien, poule, eau. Bravo. Le foin sent encore bon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honorine a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Elle a dit le nom. Chien. Poule. Eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a entendu un son. Elle a dit le nom. Chien. Poule. Eau. Tu as nommé le son ? Oui, papa. Bravo. Le chien respire tout près. Victorina pose la main sur le bois du portail. Il est rêche. Oui. On entend un son. On dit le nom. Le chien. Oui. L'eau tremble encore dans l'auge. Elle tremble. Oui. On a entendu des sons. On a dit les noms. Chien, poule, eau. Bravo. Le foin sent encore bon.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,7 +1749,6 @@
 papa|Tu as nommé le son ?
 enfant-f|Oui, papa.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Le chien respire tout près.
 narrateur|Victorina pose la main sur le bois du portail.
 enfant-f|Il est rêche.
@@ -1804,7 +1801,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le seau. Honorine écoute encore.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range le seau ? Oui. Papa range le seau contre le mur. Victorina écoute encore. Une poule rentre sous le hangar. Tu as fini d'écouter la cour ? Oui, papa. Merci. Bravo. Le collier du chien cliquette une dernière fois. La paille reste collée au portail. Tu as nommé le son, Victorina. Oui. Les pierres de la cour restent fraîches. Le chien suit jusqu'au hangar.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1952,7 +1949,6 @@
 narrateur|Le chien suit jusqu'au hangar.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1977,12 +1973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le nom. Oui. Chien, poule, eau. Bravo, Victorina. La cour redevient calme. L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Chien, poule, eau. Bravo, Victorina. La cour redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le nom. Oui. Chien, poule, eau. Bravo, Victorina. La cour redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2121,11 +2117,9 @@
 papa|Oui.
 papa|Chien, poule, eau.
 papa|Bravo, Victorina.
-narrateur|La cour redevient calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La cour redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2144,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2189,6 +2183,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-09.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Honorine, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
